--- a/expense.xlsx
+++ b/expense.xlsx
@@ -44,19 +44,13 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
     </border>
     <border>
       <left style="double">
@@ -76,15 +70,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -465,42 +453,42 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>S.no</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>mode</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>valueDate</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>narration</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Balance</t>
         </is>
       </c>
-      <c r="H1" s="2" t="n"/>
+      <c r="H1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -529,7 +517,7 @@
           <t>GAS FILLING STATION</t>
         </is>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="G2" s="2" t="n">
         <v>-1519.390000000014</v>
       </c>
     </row>
@@ -611,6 +599,9 @@
           <t>31-07-2023</t>
         </is>
       </c>
+      <c r="F5" t="n">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -8614,6 +8605,9 @@
           <t>16-11-2023</t>
         </is>
       </c>
+      <c r="F291" t="n">
+        <v/>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -11632,6 +11626,9 @@
         <is>
           <t>21-12-2023</t>
         </is>
+      </c>
+      <c r="F399" t="n">
+        <v/>
       </c>
     </row>
     <row r="400">
@@ -28099,42 +28096,42 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>S.no</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>mode</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>valueDate</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>narration</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Total Debit</t>
         </is>
       </c>
-      <c r="H1" s="2" t="n"/>
+      <c r="H1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -28163,7 +28160,7 @@
           <t>GAS FILLING STATION</t>
         </is>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="G2" s="2" t="n">
         <v>422089.9</v>
       </c>
     </row>
@@ -47628,42 +47625,42 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>S.no</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>mode</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>valueDate</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>narration</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Total Credit</t>
         </is>
       </c>
-      <c r="H1" s="2" t="n"/>
+      <c r="H1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -47690,7 +47687,7 @@
       <c r="F2" t="n">
         <v/>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="G2" s="2" t="n">
         <v>420570.51</v>
       </c>
     </row>

--- a/expense.xlsx
+++ b/expense.xlsx
@@ -18,7 +18,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -44,7 +46,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -66,14 +68,49 @@
         <color rgb="00a5a5e6"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="double">
+        <color rgb="00a5a5e6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="double">
+        <color rgb="00a5a5e6"/>
+      </right>
+      <top style="double">
+        <color rgb="00a5a5e6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="double">
+        <color rgb="00a5a5e6"/>
+      </right>
+      <top style="double">
+        <color rgb="00a5a5e6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00a5a5e6"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -439,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H986"/>
+  <dimension ref="A1:H987"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -488,7 +525,7 @@
           <t>Balance</t>
         </is>
       </c>
-      <c r="H1" s="1" t="n"/>
+      <c r="H1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -599,9 +636,6 @@
           <t>31-07-2023</t>
         </is>
       </c>
-      <c r="F5" t="n">
-        <v/>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -8605,9 +8639,6 @@
           <t>16-11-2023</t>
         </is>
       </c>
-      <c r="F291" t="n">
-        <v/>
-      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -11627,9 +11658,6 @@
           <t>21-12-2023</t>
         </is>
       </c>
-      <c r="F399" t="n">
-        <v/>
-      </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -28064,6 +28092,32 @@
       <c r="F986" t="inlineStr">
         <is>
           <t>UPI/4517</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="n">
+        <v>986</v>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="C987" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="D987" t="n">
+        <v>500</v>
+      </c>
+      <c r="E987" s="4" t="n">
+        <v>46176</v>
+      </c>
+      <c r="F987" t="inlineStr">
+        <is>
+          <t>Recharge</t>
         </is>
       </c>
     </row>
@@ -28082,7 +28136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H696"/>
+  <dimension ref="A1:H697"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -28131,7 +28185,7 @@
           <t>Total Debit</t>
         </is>
       </c>
-      <c r="H1" s="1" t="n"/>
+      <c r="H1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -47593,6 +47647,32 @@
       <c r="F696" t="inlineStr">
         <is>
           <t>UPI/4517</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="n">
+        <v>986</v>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="D697" t="n">
+        <v>500</v>
+      </c>
+      <c r="E697" s="4" t="n">
+        <v>46176</v>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>Recharge</t>
         </is>
       </c>
     </row>
@@ -47660,7 +47740,7 @@
           <t>Total Credit</t>
         </is>
       </c>
-      <c r="H1" s="1" t="n"/>
+      <c r="H1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -47684,9 +47764,6 @@
           <t>31-07-2023</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v/>
-      </c>
       <c r="G2" s="2" t="n">
         <v>420570.51</v>
       </c>
@@ -50513,9 +50590,6 @@
           <t>16-11-2023</t>
         </is>
       </c>
-      <c r="F103" t="n">
-        <v/>
-      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -51574,9 +51648,6 @@
         <is>
           <t>21-12-2023</t>
         </is>
-      </c>
-      <c r="F141" t="n">
-        <v/>
       </c>
     </row>
     <row r="142">
